--- a/holiday_forms/009_holiday_event_item_sign_up--holiday_forms.xlsx
+++ b/holiday_forms/009_holiday_event_item_sign_up--holiday_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'gluten_free'}</t>
+          <t>gluten_free</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Gluten Free'}</t>
+          <t>Gluten Free</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fruits'}</t>
+          <t>fruits</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fruits'}</t>
+          <t>Fruits</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'vegetables'}</t>
+          <t>vegetables</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Vegetables'}</t>
+          <t>Vegetables</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'dairy'}</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Dairy'}</t>
+          <t>Dairy</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'meats'}</t>
+          <t>meats</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Meats'}</t>
+          <t>Meats</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'desserts'}</t>
+          <t>desserts</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Desserts'}</t>
+          <t>Desserts</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'host'}</t>
+          <t>host</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Host'}</t>
+          <t>Host</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'guest'}</t>
+          <t>guest</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Guest'}</t>
+          <t>Guest</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
